--- a/SOL/Facturacion_Monotributo_SOL_2026.xlsx
+++ b/SOL/Facturacion_Monotributo_SOL_2026.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Facturación 2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detalle factura 00001-00000027" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +44,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,20 +103,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,33 +483,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Facturación Monotributo — Sol 2026</t>
+          <t>Facturación Monotributo — Sol 2026 (SANES MARIA SOLEDAD · CUIT 27-29039079-1)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Registro de facturas emitidas (monotributo). No es gasto CIUDAD ni Almacén. Cobros van a Reserva UDESA / Transferencias recibidas cuando figuren en extracto MP.</t>
+          <t>Fuente: PDF ARCA Factura C. No es gasto CIUDAD ni Almacén. Cobros → Reserva UDESA / Transferencias recibidas cuando figuren en extracto MP.</t>
         </is>
       </c>
     </row>
@@ -514,52 +524,67 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Período servicio</t>
+          <t>Período desde</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Período hasta</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Pvta</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Importe ARS</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Vto CAE</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Estado cobro</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Fecha cobro</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Monto cobrado ARS</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Medio cobro</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>OpID cobro</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Comentario</t>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Archivo PDF</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Concepto / comentario</t>
         </is>
       </c>
     </row>
@@ -567,36 +592,57 @@
       <c r="A5" s="4" t="n">
         <v>46226</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Junio 2026</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Aldo Pelesson / LDO Pelesson</t>
-        </is>
+      <c r="B5" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>46203</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>PELESSON ALDO OSCAR</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>23-14614689-9</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>86305115481677</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Factura monotributo Sol · servicio junio 2026 · CUIT 23146146899</t>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Honorarios profesionales · control interno / políticas y procedimientos · Consultoría de sistemas · Comp. 00001-00000027</t>
         </is>
       </c>
     </row>
@@ -606,10 +652,10 @@
           <t>Totales</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="I7" s="8" t="n">
         <v>4900000</v>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>1 factura · PENDIENTE de cobro</t>
         </is>
@@ -617,8 +663,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -630,12 +676,325 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Factura C 00001-00000027 — datos oficiales ARCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Emisor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SANES MARIA SOLEDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>CUIT emisor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>27-29039079-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Condición IVA emisor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Responsable Monotributo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Domicilio comercial</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>O'Higgins 2219 Piso:8 - Ciudad de Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Tipo comprobante</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FACTURA C (COD. 011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Punto de venta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>00000027</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Fecha de emisión</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Período facturado</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-01 a 2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Fecha vto. pago</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Condición de venta</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Otros medios de pago electrónico</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PELESSON ALDO OSCAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>CUIT cliente</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>23-14614689-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Domicilio cliente</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25 De Mayo 487 Piso:2 - Capital Federal, CABA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Condición IVA cliente</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Honorarios profesionales por asesoramiento para la implementación de mejoras en el marco de control interno, políticas y procedimientos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Actividad / leyenda</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Consultoría de sistemas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1 unidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Precio unitario / Subtotal / Total</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>4900000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Importe otros tributos</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>CAE N°</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>86305115481677</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Fecha vto. CAE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Estado cobro</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Archivo PDF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,17 +1005,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Comp.</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Facturado ARS</t>
         </is>
@@ -665,7 +1029,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aldo Pelesson / LDO Pelesson</t>
+          <t>PELESSON ALDO OSCAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,22 +1037,27 @@
           <t>23-14614689-9</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00001-00000027</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>4900000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Importe ARS</t>
         </is>
@@ -703,7 +1072,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <v>4900000</v>
       </c>
     </row>
@@ -730,9 +1099,21 @@
         <v>4900000</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PDF fuente</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SOL/Facturacion_Monotributo_SOL_2026.xlsx
+++ b/SOL/Facturacion_Monotributo_SOL_2026.xlsx
@@ -63,7 +63,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +116,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -498,8 +499,8 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="52" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -512,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: PDF ARCA Factura C. No es gasto CIUDAD ni Almacén. Cobros → Reserva UDESA / Transferencias recibidas cuando figuren en extracto MP.</t>
+          <t>Fuente: PDF ARCA Factura C. Cobro 23/07/2026 confirmado por Sol vía MP (OpID pendiente de próximo extracto).</t>
         </is>
       </c>
     </row>
@@ -579,12 +580,12 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Archivo PDF</t>
+          <t>Fecha cobro</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Concepto / comentario</t>
+          <t>Archivo PDF / comentario</t>
         </is>
       </c>
     </row>
@@ -632,17 +633,15 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
-        </is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>46226</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>Honorarios profesionales · control interno / políticas y procedimientos · Consultoría de sistemas · Comp. 00001-00000027</t>
+          <t>MP · $4.900.000 · OpID pendiente extracto · PDF _inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
         </is>
       </c>
     </row>
@@ -657,7 +656,7 @@
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>1 factura · PENDIENTE de cobro</t>
+          <t>1 factura · COBRADA</t>
         </is>
       </c>
     </row>
@@ -676,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -686,7 +685,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Factura C 00001-00000027 — datos oficiales ARCA</t>
+          <t>Factura C 00001-00000027 — datos oficiales ARCA + cobro</t>
         </is>
       </c>
     </row>
@@ -717,258 +716,162 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Condición IVA emisor</t>
+          <t>Tipo comprobante</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Responsable Monotributo</t>
+          <t>FACTURA C (COD. 011) 00001-00000027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Domicilio comercial</t>
+          <t>Fecha de emisión</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O'Higgins 2219 Piso:8 - Ciudad de Buenos Aires</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Tipo comprobante</t>
+          <t>Período facturado</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FACTURA C (COD. 011)</t>
+          <t>2026-06-01 a 2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Punto de venta</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>00001</t>
+          <t>PELESSON ALDO OSCAR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Número</t>
+          <t>CUIT cliente</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>00000027</t>
+          <t>23-14614689-9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Fecha de emisión</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+          <t>Importe Total</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>4900000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Período facturado</t>
+          <t>CAE N°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-01 a 2026-06-30</t>
+          <t>86305115481677</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Fecha vto. pago</t>
+          <t>Fecha vto. CAE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Condición de venta</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Otros medios de pago electrónico</t>
+          <t>Estado cobro</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Fecha cobro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PELESSON ALDO OSCAR</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>CUIT cliente</t>
+          <t>Medio cobro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23-14614689-9</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Domicilio cliente</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>25 De Mayo 487 Piso:2 - Capital Federal, CABA</t>
-        </is>
+          <t>Monto cobrado</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>4900000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Condición IVA cliente</t>
+          <t>OpID cobro</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IVA Responsable Inscripto</t>
+          <t>PENDIENTE próximo extracto MP (último extracto corta 2026-07-18)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Concepto</t>
+          <t>Archivo PDF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>Honorarios profesionales por asesoramiento para la implementación de mejoras en el marco de control interno, políticas y procedimientos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Actividad / leyenda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Consultoría de sistemas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1 unidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Precio unitario / Subtotal / Total</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>4900000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Importe otros tributos</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>CAE N°</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>86305115481677</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Fecha vto. CAE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Estado cobro</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Archivo PDF</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
         <is>
           <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
         </is>
@@ -1005,22 +908,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Comp.</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Facturado ARS</t>
         </is>
@@ -1047,17 +950,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Importe ARS</t>
         </is>
@@ -1070,10 +973,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>4900000</v>
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1083,10 +986,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>4900000</v>
       </c>
     </row>
     <row r="10">
@@ -1102,12 +1005,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PDF fuente</t>
+          <t>Cobro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
+          <t>2026-07-23 · Mercado Pago · OpID pendiente extracto</t>
         </is>
       </c>
     </row>

--- a/SOL/Facturacion_Monotributo_SOL_2026.xlsx
+++ b/SOL/Facturacion_Monotributo_SOL_2026.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,8 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="70" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -513,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: PDF ARCA Factura C. Cobro 23/07/2026 confirmado por Sol vía MP (OpID pendiente de próximo extracto).</t>
+          <t>Cobro 23/07/2026 MP → destino Reserva Chris (UDESA). OpID pendiente de próximo extracto.</t>
         </is>
       </c>
     </row>
@@ -585,7 +586,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Archivo PDF / comentario</t>
+          <t>Destino reserva</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>PDF / comentario</t>
         </is>
       </c>
     </row>
@@ -641,7 +647,12 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>MP · $4.900.000 · OpID pendiente extracto · PDF _inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
+          <t>Reserva Chris (UDESA)</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf · OpID pendiente extracto</t>
         </is>
       </c>
     </row>
@@ -656,14 +667,14 @@
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>1 factura · COBRADA</t>
+          <t>1 factura · COBRADA → Reserva Chris</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -675,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -685,7 +696,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Factura C 00001-00000027 — datos oficiales ARCA + cobro</t>
+          <t>Factura C 00001-00000027 — ARCA + cobro → Reserva Chris</t>
         </is>
       </c>
     </row>
@@ -856,22 +867,34 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>OpID cobro</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PENDIENTE próximo extracto MP (último extracto corta 2026-07-18)</t>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Reserva Chris (Dinero reservado Chris / UDESA)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>OpID cobro/reserva</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PENDIENTE próximo extracto MP (último extracto corta 2026-07-18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>Archivo PDF</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
         </is>
@@ -894,7 +917,7 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -982,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COBRADO</t>
+          <t>COBRADO → Reserva Chris</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1005,12 +1028,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cobro</t>
+          <t>Destino cobro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-23 · Mercado Pago · OpID pendiente extracto</t>
+          <t>Reserva Chris (UDESA) · Dinero reservado Chris</t>
         </is>
       </c>
     </row>

--- a/SOL/Facturacion_Monotributo_SOL_2026.xlsx
+++ b/SOL/Facturacion_Monotributo_SOL_2026.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Facturación 2026" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Detalle factura 00001-00000027" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detalle factura 00001-00000028" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +44,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -76,8 +91,23 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCF3CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -99,16 +129,30 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +163,20 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,172 +545,231 @@
   <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Facturación Monotributo — Sol 2026 (SANES MARIA SOLEDAD · CUIT 27-29039079-1)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cobro 23/07/2026 MP → destino Reserva Chris (UDESA). OpID pendiente de próximo extracto.</t>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Última carga: Factura C 00001-00000028 · FUNDACION UNIVERSIDAD DE PALERMO · $3.250.000 · 05/08/2026 · PENDIENTE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Fecha factura</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Período desde</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Período hasta</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Pvta</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Importe ARS</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>CAE</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Vto CAE</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>Estado cobro</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>Fecha cobro</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>Destino reserva</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t>PDF / comentario</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="18" t="n">
         <v>46226</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="18" t="n">
         <v>46174</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="18" t="n">
         <v>46203</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>FACTURA C</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>PELESSON ALDO OSCAR</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>23-14614689-9</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="20" t="n">
         <v>4900000</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>86305115481677</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="18" t="n">
         <v>46236</v>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>COBRADO</t>
         </is>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="18" t="n">
         <v>46226</v>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="19" t="inlineStr">
         <is>
           <t>Reserva Chris (UDESA)</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf · OpID pendiente extracto</t>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf · COBRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>86316971456619</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>46249</v>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000028.pdf · PENDIENTE</t>
         </is>
       </c>
     </row>
@@ -662,20 +779,16 @@
           <t>Totales</t>
         </is>
       </c>
-      <c r="I7" s="8" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>1 factura · COBRADA → Reserva Chris</t>
+      <c r="I7" s="23" t="n">
+        <v>8150000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2 facturas · 1 COBRADA(S) · 1 PENDIENTE(S)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -686,22 +799,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Factura C 00001-00000027 — ARCA + cobro → Reserva Chris</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Emisor</t>
         </is>
@@ -713,7 +826,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>CUIT emisor</t>
         </is>
@@ -725,7 +838,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Tipo comprobante</t>
         </is>
@@ -737,7 +850,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Fecha de emisión</t>
         </is>
@@ -749,7 +862,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Período facturado</t>
         </is>
@@ -761,7 +874,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -773,7 +886,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CUIT cliente</t>
         </is>
@@ -785,125 +898,194 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Domicilio cliente</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>25 De Mayo 487 Piso:2 - Capital Federal, Ciudad de Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Condición IVA cliente</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IVA Responsable Inscripto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Honorarios profesionales por asesoramiento para la implementación de mejoras en el marco de control interno, políticas y procedimientos (Consultoría de sistemas.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Importe Total</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B13" s="24" t="n">
         <v>4900000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>CAE N°</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>86305115481677</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Fecha vto. CAE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Vto. pago</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Condición de venta</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Otros medios de pago electrónico</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Estado cobro</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>COBRADO</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Fecha cobro</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Medio cobro</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Mercado Pago</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Monto cobrado</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B21" t="n">
         <v>4900000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Reserva Chris (Dinero reservado Chris / UDESA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Reserva Chris (UDESA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>OpID cobro/reserva</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PENDIENTE próximo extracto MP (último extracto corta 2026-07-18)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Archivo PDF</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Emisor SANES MARIA SOLEDAD CUIT 27-29039079-1 · Comp. 00001-00000027 · PDF ARCA · Abonada 23/07/2026 con MP · dinero a Dinero reservado Chris · OpID pendiente de próximo extracto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -914,41 +1096,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Factura C 00001-00000028 — ARCA · cobro PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Emisor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SANES MARIA SOLEDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>CUIT emisor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>27-29039079-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tipo comprobante</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FACTURA C (COD. 011) 00001-00000028</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Fecha de emisión</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Período facturado</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01 a 2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CUIT cliente</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Domicilio cliente</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bravo Mario 1050 - Capital Federal, Ciudad de Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Condición IVA cliente</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IVA Sujeto Exento</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Honorarios profesionales Julio (Consultoría de sistemas.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Importe Total</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>CAE N°</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>86316971456619</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Fecha vto. CAE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Vto. pago</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Condición de venta</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Otros medios de pago electrónico</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Estado cobro</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Fecha cobro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Medio cobro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Monto cobrado</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>— (sin ruteo a reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>OpID cobro/reserva</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Archivo PDF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000028.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Emisor SANES MARIA SOLEDAD CUIT 27-29039079-1 · Comp. 00001-00000028 · PDF ARCA · Cliente FUNDACION UNIVERSIDAD DE PALERMO · Período julio 2026 · Cobro PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Resumen Facturación Monotributo Sol</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Comp.</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>Facturado ARS</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -968,79 +1455,115 @@
           <t>00001-00000027</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="24" t="n">
         <v>4900000</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00001-00000028</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Importe ARS</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>COBRADO → Reserva Chris</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="24" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="24" t="n">
         <v>4900000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Total facturado</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>4900000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Destino cobro</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Reserva Chris (UDESA) · Dinero reservado Chris</t>
+      <c r="C11" s="28" t="n">
+        <v>8150000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00001-00000027 → Reserva Chris (UDESA) · COBRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00001-00000028 → FUNDACION UNIVERSIDAD DE PALERMO · PENDIENTE (no es Reserva Chris)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SOL/Facturacion_Monotributo_SOL_2026.xlsx
+++ b/SOL/Facturacion_Monotributo_SOL_2026.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Facturación 2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Detalle factura 00001-00000027" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Detalle factura 00001-00000028" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Resumen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Por cliente" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detalle 00001-00000027" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Detalle 00001-00000028" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumen" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -106,8 +111,23 @@
         <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5D8DC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -143,11 +163,12 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +198,18 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,24 +575,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,82 +607,92 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Última carga: Factura C 00001-00000028 · FUNDACION UNIVERSIDAD DE PALERMO · $3.250.000 · 05/08/2026 · PENDIENTE</t>
+          <t>Historial completo planilla Sol + PDFs ARCA 27/28 · 13 comprobantes · Total neto $38,550,000 · Nros 26/27 Aldo corregidos vs planilla (prevalece PDF ARCA)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Fecha factura</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Flag fecha</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Período desde</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Período hasta</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Pvta</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t>Importe ARS</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="L4" s="29" t="inlineStr">
         <is>
           <t>CAE</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t>Vto CAE</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="N4" s="29" t="inlineStr">
         <is>
           <t>Estado cobro</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
+      <c r="O4" s="29" t="inlineStr">
         <is>
           <t>Fecha cobro</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="P4" s="29" t="inlineStr">
         <is>
           <t>Destino reserva</t>
         </is>
       </c>
-      <c r="O4" s="17" t="inlineStr">
+      <c r="Q4" s="29" t="inlineStr">
         <is>
           <t>PDF / comentario</t>
         </is>
@@ -655,140 +700,1111 @@
     </row>
     <row r="5">
       <c r="A5" s="18" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>46174</v>
+        <v>46032</v>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
       </c>
       <c r="C5" s="18" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
+        <v>45992</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>46022</v>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>FACTURA C</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>PELESSON ALDO OSCAR</t>
-        </is>
+      <c r="G5" s="19" t="n">
+        <v>17</v>
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>23-14614689-9</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>4900000</v>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>86305115481677</t>
-        </is>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>46236</v>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>COBRADO</t>
-        </is>
-      </c>
-      <c r="M5" s="18" t="n">
-        <v>46226</v>
-      </c>
-      <c r="N5" s="19" t="inlineStr">
-        <is>
-          <t>Reserva Chris (UDESA)</t>
-        </is>
-      </c>
-      <c r="O5" s="19" t="inlineStr">
-        <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf · COBRADO</t>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q5" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000017 · Período dic-2025 · Fecha emisión RE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>46053</v>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q6" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000018 · Período ene-2026 · Fecha emisión RE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="18" t="n">
+        <v>46054</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>2870000</v>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q7" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000019 · Período feb-2026 · Emisión 10/03/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="18" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>2880000</v>
+      </c>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="19" t="n"/>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>ANULADA por NC</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000020 · Anulada por NC C 00001-00000001 mis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="18" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>NOTA DE CREDITO C</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>-2880000</v>
+      </c>
+      <c r="L9" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · NC C 00001-00000001 · Anula FC 00001-00000020 · 02/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="18" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>2950000</v>
+      </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000021 · Reemplazo tras NC · Emisión 02/04/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000022 · Período abr-2026 · Emisión 04/05/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>PELESSON ALDO OSCAR</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>23-14614689-9</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="n">
+        <v>46157</v>
+      </c>
+      <c r="P12" s="19" t="inlineStr">
+        <is>
+          <t>Reserva Chris (UDESA)</t>
+        </is>
+      </c>
+      <c r="Q12" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Nro asignado 00001-00000026 (planilla Sol decía 27; PDF AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="18" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000024 · Período may-2026 · Emisión 08/06/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="18" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>PELESSON ALDO OSCAR</t>
+        </is>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>23-14614689-9</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="n">
+        <v>46185</v>
+      </c>
+      <c r="P14" s="19" t="inlineStr">
+        <is>
+          <t>Reserva Chris (UDESA)</t>
+        </is>
+      </c>
+      <c r="Q14" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000023 · Emisión 17/06/2026 · Cobro MP 12/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="30" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="19" t="inlineStr">
+        <is>
+          <t>Fuente planilla Sol · Comp. 00001-00000025 · Período jun-2026 · Fecha emisión RE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="18" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>PELESSON ALDO OSCAR</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>23-14614689-9</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>86305115481677</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>46236</v>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="n">
+        <v>46226</v>
+      </c>
+      <c r="P16" s="19" t="inlineStr">
+        <is>
+          <t>Reserva Chris (UDESA)</t>
+        </is>
+      </c>
+      <c r="Q16" s="19" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf · PDF ARCA oficial · Comp. 00001-00000027 · Planilla Sol lo listó como 26; prevale</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n">
         <v>46239</v>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="18" t="n">
         <v>46204</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="D17" s="18" t="n">
         <v>46234</v>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>FACTURA C</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="F17" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="G17" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
         <is>
           <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="J17" s="19" t="inlineStr">
         <is>
           <t>33-62010144-9</t>
         </is>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="K17" s="20" t="n">
         <v>3250000</v>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="L17" s="19" t="inlineStr">
         <is>
           <t>86316971456619</t>
         </is>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="M17" s="18" t="n">
         <v>46249</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="N17" s="22" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="M6" s="19" t="n"/>
-      <c r="N6" s="19" t="inlineStr">
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O6" s="19" t="inlineStr">
-        <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000028.pdf · PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="Q17" s="19" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000028.pdf · PDF ARCA oficial · Comp. 00001-00000028 · Cliente FUNDACION UNIVERSIDAD DE PALER</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Totales</t>
         </is>
       </c>
-      <c r="I7" s="23" t="n">
-        <v>8150000</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2 facturas · 1 COBRADA(S) · 1 PENDIENTE(S)</t>
-        </is>
-      </c>
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
+      <c r="H18" s="39" t="n"/>
+      <c r="I18" s="39" t="n"/>
+      <c r="J18" s="39" t="n"/>
+      <c r="K18" s="40" t="n">
+        <v>38550000</v>
+      </c>
+      <c r="L18" s="39" t="n"/>
+      <c r="M18" s="39" t="n"/>
+      <c r="N18" s="39" t="inlineStr">
+        <is>
+          <t>13 comps · 3 COBRADO · 1 PENDIENTE · 7 REVISAR cobro</t>
+        </is>
+      </c>
+      <c r="O18" s="39" t="n"/>
+      <c r="P18" s="39" t="n"/>
+      <c r="Q18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="n"/>
+      <c r="B19" s="39" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="39" t="n"/>
+      <c r="J19" s="39" t="n"/>
+      <c r="K19" s="39" t="n"/>
+      <c r="L19" s="39" t="n"/>
+      <c r="M19" s="39" t="n"/>
+      <c r="N19" s="39" t="n"/>
+      <c r="O19" s="39" t="n"/>
+      <c r="P19" s="39" t="n"/>
+      <c r="Q19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="n"/>
+      <c r="B20" s="39" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="39" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="39" t="n"/>
+      <c r="J20" s="39" t="n"/>
+      <c r="K20" s="39" t="n"/>
+      <c r="L20" s="39" t="n"/>
+      <c r="M20" s="39" t="n"/>
+      <c r="N20" s="39" t="n"/>
+      <c r="O20" s="39" t="n"/>
+      <c r="P20" s="39" t="n"/>
+      <c r="Q20" s="39" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="n"/>
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="39" t="n"/>
+      <c r="L21" s="39" t="n"/>
+      <c r="M21" s="39" t="n"/>
+      <c r="N21" s="39" t="n"/>
+      <c r="O21" s="39" t="n"/>
+      <c r="P21" s="39" t="n"/>
+      <c r="Q21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="n"/>
+      <c r="B22" s="39" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
+      <c r="H22" s="39" t="n"/>
+      <c r="I22" s="39" t="n"/>
+      <c r="J22" s="39" t="n"/>
+      <c r="K22" s="39" t="n"/>
+      <c r="L22" s="39" t="n"/>
+      <c r="M22" s="39" t="n"/>
+      <c r="N22" s="39" t="n"/>
+      <c r="O22" s="39" t="n"/>
+      <c r="P22" s="39" t="n"/>
+      <c r="Q22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="n"/>
+      <c r="B23" s="39" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="39" t="n"/>
+      <c r="K23" s="39" t="n"/>
+      <c r="L23" s="39" t="n"/>
+      <c r="M23" s="39" t="n"/>
+      <c r="N23" s="39" t="n"/>
+      <c r="O23" s="39" t="n"/>
+      <c r="P23" s="39" t="n"/>
+      <c r="Q23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="n"/>
+      <c r="B24" s="39" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="39" t="n"/>
+      <c r="M24" s="39" t="n"/>
+      <c r="N24" s="39" t="n"/>
+      <c r="O24" s="39" t="n"/>
+      <c r="P24" s="39" t="n"/>
+      <c r="Q24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="n"/>
+      <c r="B25" s="39" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="39" t="n"/>
+      <c r="K25" s="39" t="n"/>
+      <c r="L25" s="39" t="n"/>
+      <c r="M25" s="39" t="n"/>
+      <c r="N25" s="39" t="n"/>
+      <c r="O25" s="39" t="n"/>
+      <c r="P25" s="39" t="n"/>
+      <c r="Q25" s="39" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="n"/>
+      <c r="B26" s="39" t="n"/>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
+      <c r="H26" s="39" t="n"/>
+      <c r="I26" s="39" t="n"/>
+      <c r="J26" s="39" t="n"/>
+      <c r="K26" s="39" t="n"/>
+      <c r="L26" s="39" t="n"/>
+      <c r="M26" s="39" t="n"/>
+      <c r="N26" s="39" t="n"/>
+      <c r="O26" s="39" t="n"/>
+      <c r="P26" s="39" t="n"/>
+      <c r="Q26" s="39" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="n"/>
+      <c r="B27" s="39" t="n"/>
+      <c r="C27" s="39" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+      <c r="H27" s="39" t="n"/>
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="39" t="n"/>
+      <c r="K27" s="39" t="n"/>
+      <c r="L27" s="39" t="n"/>
+      <c r="M27" s="39" t="n"/>
+      <c r="N27" s="39" t="n"/>
+      <c r="O27" s="39" t="n"/>
+      <c r="P27" s="39" t="n"/>
+      <c r="Q27" s="39" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="n"/>
+      <c r="B28" s="39" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
+      <c r="H28" s="39" t="n"/>
+      <c r="I28" s="39" t="n"/>
+      <c r="J28" s="39" t="n"/>
+      <c r="K28" s="39" t="n"/>
+      <c r="L28" s="39" t="n"/>
+      <c r="M28" s="39" t="n"/>
+      <c r="N28" s="39" t="n"/>
+      <c r="O28" s="39" t="n"/>
+      <c r="P28" s="39" t="n"/>
+      <c r="Q28" s="39" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="n"/>
+      <c r="B29" s="39" t="n"/>
+      <c r="C29" s="39" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="39" t="n"/>
+      <c r="H29" s="39" t="n"/>
+      <c r="I29" s="39" t="n"/>
+      <c r="J29" s="39" t="n"/>
+      <c r="K29" s="39" t="n"/>
+      <c r="L29" s="39" t="n"/>
+      <c r="M29" s="39" t="n"/>
+      <c r="N29" s="39" t="n"/>
+      <c r="O29" s="39" t="n"/>
+      <c r="P29" s="39" t="n"/>
+      <c r="Q29" s="39" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="n"/>
+      <c r="B30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="39" t="n"/>
+      <c r="J30" s="39" t="n"/>
+      <c r="K30" s="39" t="n"/>
+      <c r="L30" s="39" t="n"/>
+      <c r="M30" s="39" t="n"/>
+      <c r="N30" s="39" t="n"/>
+      <c r="O30" s="39" t="n"/>
+      <c r="P30" s="39" t="n"/>
+      <c r="Q30" s="39" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -799,290 +1815,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>Factura C 00001-00000027 — ARCA + cobro → Reserva Chris</t>
+          <t>Resumen por cliente / período</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Emisor</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SANES MARIA SOLEDAD</t>
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>CUIT</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>Comprobantes</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>Neto ARS</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>Cobrado ARS</t>
+        </is>
+      </c>
+      <c r="F3" s="33" t="inlineStr">
+        <is>
+          <t>Pendiente/REVISAR ARS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>CUIT emisor</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aldo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27-29039079-1</t>
-        </is>
+          <t>23-14614689-9</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="24" t="n">
+        <v>14650000</v>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>14650000</v>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Tipo comprobante</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FACTURA C (COD. 011) 00001-00000027</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Fecha de emisión</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Período facturado</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-01 a 2026-06-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PELESSON ALDO OSCAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>CUIT cliente</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>23-14614689-9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Domicilio cliente</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>25 De Mayo 487 Piso:2 - Capital Federal, Ciudad de Buenos Aires</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Condición IVA cliente</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IVA Responsable Inscripto</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Honorarios profesionales por asesoramiento para la implementación de mejoras en el marco de control interno, políticas y procedimientos (Consultoría de sistemas.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Importe Total</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="n">
-        <v>4900000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>CAE N°</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>86305115481677</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Fecha vto. CAE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Vto. pago</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Condición de venta</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Otros medios de pago electrónico</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Estado cobro</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>COBRADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Fecha cobro</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Medio cobro</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mercado Pago</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Monto cobrado</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4900000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Reserva Chris (UDESA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>OpID cobro/reserva</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Archivo PDF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Comentario</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Emisor SANES MARIA SOLEDAD CUIT 27-29039079-1 · Comp. 00001-00000027 · PDF ARCA · Abonada 23/07/2026 con MP · dinero a Dinero reservado Chris · OpID pendiente de próximo extracto</t>
-        </is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>23900000</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>23900000</v>
       </c>
     </row>
   </sheetData>
@@ -1096,17 +1924,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>Factura C 00001-00000028 — ARCA · cobro PENDIENTE</t>
+          <t>FACTURA C 00001-00000027 — Aldo</t>
         </is>
       </c>
     </row>
@@ -1137,250 +1965,200 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Tipo comprobante</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FACTURA C (COD. 011) 00001-00000028</t>
+          <t>FACTURA C 00001-00000027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Fecha de emisión</t>
+          <t>Fecha emisión</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Período facturado</t>
+          <t>Período</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01 a 2026-07-31</t>
+          <t>2026-06-01 a 2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Grupo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+          <t>Aldo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>CUIT cliente</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33-62010144-9</t>
+          <t>PELESSON ALDO OSCAR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Domicilio cliente</t>
+          <t>CUIT cliente</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bravo Mario 1050 - Capital Federal, Ciudad de Buenos Aires</t>
+          <t>23-14614689-9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Condición IVA cliente</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IVA Sujeto Exento</t>
-        </is>
+          <t>Importe</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>4900000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Concepto</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Honorarios profesionales Julio (Consultoría de sistemas.)</t>
+          <t>86305115481677</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Importe Total</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="n">
-        <v>3250000</v>
+          <t>Vto CAE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CAE N°</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>86316971456619</t>
+          <t>Estado cobro</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Fecha vto. CAE</t>
+          <t>Fecha cobro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Vto. pago</t>
+          <t>Medio cobro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Condición de venta</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Otros medios de pago electrónico</t>
-        </is>
+          <t>Monto cobrado</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4900000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Estado cobro</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>OpID</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Fecha cobro</t>
+          <t>Destino</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reserva Chris (UDESA)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Medio cobro</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000027.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Monto cobrado</t>
+          <t>Comentario</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>— (sin ruteo a reserva)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>OpID cobro/reserva</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Archivo PDF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000028.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Comentario</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Emisor SANES MARIA SOLEDAD CUIT 27-29039079-1 · Comp. 00001-00000028 · PDF ARCA · Cliente FUNDACION UNIVERSIDAD DE PALERMO · Período julio 2026 · Cobro PENDIENTE</t>
+          <t>PDF ARCA oficial · Comp. 00001-00000027 · Planilla Sol lo listó como 26; prevalece PDF · Abonada 23/07/2026 MP → Reserva Chris · OpID pendiente extracto</t>
         </is>
       </c>
     </row>
@@ -1395,45 +2173,308 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>Resumen Facturación Monotributo Sol</t>
+          <t>FACTURA C 00001-00000028 — Palermo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Emisor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SANES MARIA SOLEDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>CUIT emisor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>27-29039079-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FACTURA C 00001-00000028</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Fecha emisión</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01 a 2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>CUIT</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>CUIT cliente</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>33-62010144-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Importe</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>86316971456619</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Vto CAE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Estado cobro</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Fecha cobro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Medio cobro</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Monto cobrado</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>OpID</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>_inbox/facturas_monotributo/27290390791_011_00001_00000028.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PDF ARCA oficial · Comp. 00001-00000028 · Cliente FUNDACION UNIVERSIDAD DE PALERMO · Período julio 2026 · Cobro PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Resumen Facturación Monotributo Sol 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>Comp.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
-        <is>
-          <t>Facturado ARS</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="F3" s="33" t="inlineStr">
+        <is>
+          <t>Importe ARS</t>
+        </is>
+      </c>
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -1442,124 +2483,483 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PELESSON ALDO OSCAR</t>
+          <t>00001-00000017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23-14614689-9</t>
+          <t>FACTURA C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>00001-00000027</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>COBRADO</t>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>46032</v>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FUNDACION UNIVERSIDAD DE PALERMO</t>
+          <t>00001-00000018</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33-62010144-9</t>
+          <t>FACTURA C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>00001-00000028</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>46063</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00001-00000019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>46091</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>2870000</v>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Importe ARS</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00001-00000020</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>46114</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>2880000</v>
+      </c>
+      <c r="G7" s="37" t="inlineStr">
+        <is>
+          <t>ANULADA por NC</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <v>3250000</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NC-00000001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NOTA DE CREDITO C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>46114</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>-2880000</v>
+      </c>
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00001-00000021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>46114</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>2950000</v>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00001-00000022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>46146</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00001-00000026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>COBRADO</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="24" t="n">
-        <v>4900000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Total facturado</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>8150000</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00001-00000024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>46181</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notas</t>
+          <t>00001-00000023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>46190</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00001-00000027 → Reserva Chris (UDESA) · COBRADO</t>
+          <t>00001-00000025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00001-00000028 → FUNDACION UNIVERSIDAD DE PALERMO · PENDIENTE (no es Reserva Chris)</t>
+          <t>00001-00000027</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aldo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="n">
+        <v>46226</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>COBRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00001-00000028</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FACTURA C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Total neto facturado</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>38550000</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PDF oficiales: 00001-00000027 (Aldo/junio) y 00001-00000028 (Palermo/julio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Corrección: planilla Sol Aldo junio=26 / abril=27 → PDF ARCA fija junio=27; abril asignado 26 (confirmar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flag REVISAR en fecha: emisión no informada (tentativa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cobros Aldo → Reserva Chris (UDESA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Palermo cobros: REVISAR/PENDIENTE</t>
         </is>
       </c>
     </row>
